--- a/deliverables/超滤设备改造_EN.xlsx
+++ b/deliverables/超滤设备改造_EN.xlsx
@@ -326,7 +326,7 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">UF</t>
+      <t xml:space="preserve">TFF</t>
     </r>
   </si>
   <si>
@@ -516,7 +516,7 @@
     <t>TFF</t>
   </si>
   <si>
-    <t xml:space="preserve">UF</t>
+    <t xml:space="preserve">TFF</t>
   </si>
   <si>
     <r>
